--- a/store/backtest_report.xlsx
+++ b/store/backtest_report.xlsx
@@ -464,13 +464,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>542</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>71.4286</v>
+        <v>49.505</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -504,7 +504,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3.0967</v>
+        <v>0.7311</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -516,22 +516,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2036</v>
+        <v>24.1421</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.1295</v>
+        <v>13.4997</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9933</v>
+        <v>2.1517</v>
       </c>
       <c r="F5" t="n">
-        <v>25.5709</v>
+        <v>22.5543</v>
       </c>
       <c r="G5" t="n">
-        <v>30.7564</v>
+        <v>30.5135</v>
       </c>
     </row>
     <row r="6">
@@ -541,22 +541,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-6.7744</v>
+        <v>-19.883</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.2293</v>
+        <v>-4.2913</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3344</v>
+        <v>-5.1423</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.3821</v>
+        <v>-17.8404</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.8957</v>
+        <v>-15.9646</v>
       </c>
     </row>
     <row r="7">
@@ -573,7 +573,7 @@
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>4.733447</v>
+        <v>1.186539</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.283051</v>
+        <v>1.826156</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.399536</v>
+        <v>2.732686</v>
       </c>
       <c r="D8" t="n">
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>2.451528</v>
+        <v>0.5207310000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>5.280473</v>
+        <v>1.81868</v>
       </c>
       <c r="G8" t="n">
-        <v>5.375545</v>
+        <v>2.249483</v>
       </c>
     </row>
     <row r="9">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.1083</v>
+        <v>55.1914</v>
       </c>
       <c r="C9" t="n">
-        <v>-4.3741</v>
+        <v>29.3491</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.0816</v>
+        <v>4.4214</v>
       </c>
       <c r="F9" t="n">
-        <v>145.1185</v>
+        <v>51.1841</v>
       </c>
       <c r="G9" t="n">
-        <v>187.4574</v>
+        <v>71.8073</v>
       </c>
     </row>
     <row r="10">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.894638</v>
+        <v>1.855556</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.464289</v>
+        <v>2.786177</v>
       </c>
       <c r="D10" t="n">
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>3.593648</v>
+        <v>0.599473</v>
       </c>
       <c r="F10" t="n">
-        <v>5.593444</v>
+        <v>1.903048</v>
       </c>
       <c r="G10" t="n">
-        <v>6.142295</v>
+        <v>2.49384</v>
       </c>
     </row>
     <row r="11">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.263525</v>
+        <v>2.775808</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.836459</v>
+        <v>6.839218</v>
       </c>
       <c r="D11" t="n">
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>6.056502</v>
+        <v>0.859815</v>
       </c>
       <c r="F11" t="n">
-        <v>33.116122</v>
+        <v>2.868998</v>
       </c>
       <c r="G11" t="n">
-        <v>38.290203</v>
+        <v>4.497901</v>
       </c>
     </row>
     <row r="12">
@@ -688,7 +688,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>15.0533</v>
+        <v>32.1245</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -700,20 +700,20 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4215</v>
+        <v>0.4973</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7606000000000001</v>
+        <v>1.9632</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0.5031</v>
+        <v>0.491</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5238</v>
+        <v>0.5229</v>
       </c>
     </row>
     <row r="14">
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,131 +784,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>FINAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
+          <t>fast_dev</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oos_start</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
+          <t>no_plots</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>oos_end</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2022-03-22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>data_start_actual</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>n_tickers</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
+          <t>oos_start</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tickers</t>
+          <t>oos_end</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>["FPT", "VNM", "GAS"]</t>
+          <t>2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>universe</t>
+          <t>data_start_actual</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>smoke</t>
+          <t>2021-12-31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>signal_every</t>
+          <t>n_tickers</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>walk_forward</t>
-        </is>
-      </c>
-      <c r="B11" t="b">
-        <v>0</v>
+          <t>tickers</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>["ACB", "ANV", "BAF", "BCM", "BID", "BMP", "BSI", "BSR", "BVH", "BWE", "CII", "CMG", "CTD", "CTG", "CTR", "CTS", "DBC", "DCM", "DGW", "DIG", "DPM", "DSE", "DXG", "EIB", "EVF", "FPT", "FRT", "FTS", "GAS", "GEE", "GEX", "GMD", "GVR", "HAG", "HCM", "HDB", "HDG", "HHV", "HPG", "HSG", "HT1", "KBC", "KDC", "KDH", "KOS", "LPB", "MBB", "MCH", "MSB", "MSN", "MWG", "NAB", "NKG", "NLG", "NT2", "NVL", "OCB", "PAN", "PC1", "PDR", "PHR", "PLX", "PNJ", "POW", "PVD", "PVT", "REE", "SAB", "SBT", "SHB", "SIP", "SJS", "SSB", "SSI", "STB", "TAL", "TCB", "TCH", "TCX", "TPB", "VCB", "VCG", "VCI", "VCK", "VGC", "VHC", "VHM", "VIB", "VIC", "VIX", "VJC", "VND", "VNM", "VPB", "VPI", "VPL", "VPX", "VRE", "VSC", "VTP"]</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>with_fundamentals</t>
-        </is>
-      </c>
-      <c r="B12" t="b">
-        <v>0</v>
+          <t>universe</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>vn100</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>warmup_years</t>
+          <t>signal_every</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -918,103 +920,133 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>execution</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Close T+1</t>
-        </is>
+          <t>walk_forward</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>risk_sizing</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>inverse_vol_normalize then w_max cap</t>
-        </is>
+          <t>with_fundamentals</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>survivorship</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fixed/current VN100 — subject to survivorship bias</t>
-        </is>
+          <t>warmup_years</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pit_lag_days</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>90</v>
+          <t>execution</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Close T+1</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fold_sharpes</t>
+          <t>risk_sizing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>inverse_vol_normalize then w_max cap</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fold_sharpe_mean</t>
+          <t>survivorship</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fixed/current VN100 — subject to survivorship bias</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fold_sharpe_std</t>
-        </is>
+          <t>pit_lag_days</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>n_folds</t>
+          <t>fold_sharpes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ablation_steps</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>[{"layer": "B0_buyhold", "sharpe": 2.7504281603391743, "cagr": 0.5177024932850103, "max_drawdown": -0.040821256099679015, "n_trades": 0}, {"layer": "fundamental", "sharpe": 2.7504281603391743, "cagr": 0.5177024932850103, "max_drawdown": -0.040821256099679015, "n_trades": 0}, {"layer": "regime", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}, {"layer": "alpha", "sharpe": -0.2698492205220619, "cagr": -0.011221562290400944, "max_drawdown": -0.02482962035327374, "n_trades": 9}, {"layer": "risk", "sharpe": -0.5003345792385888, "cagr": -0.019873608470469484, "max_drawdown": -0.02482962035327385, "n_trades": 9}, {"layer": "B1_ta", "sharpe": 1.4985530867460732, "cagr": 0.13468353833173485, "max_drawdown": -0.0351829220317722, "n_trades": 9}, {"layer": "B2_canslim", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}]</t>
+          <t>fold_sharpe_mean</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>fold_sharpe_std</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>n_folds</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ablation_steps</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[{"layer": "B0_buyhold", "sharpe": 1.8321692424745784, "cagr": 0.5536251775534435, "max_drawdown": -0.19842368333185867, "n_trades": 0}, {"layer": "fundamental", "sharpe": 1.6093930295482695, "cagr": 0.49110361326245866, "max_drawdown": -0.214859956680571, "n_trades": 0}, {"layer": "regime", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}, {"layer": "alpha", "sharpe": 0.8521106914728611, "cagr": 0.08236888909752338, "max_drawdown": -0.04927282879075445, "n_trades": 96}, {"layer": "risk", "sharpe": 0.5207306915927736, "cagr": 0.044213977053179754, "max_drawdown": -0.051422689765345364, "n_trades": 101}, {"layer": "B1_ta", "sharpe": 2.74139086012495, "cagr": 0.2941371053925228, "max_drawdown": -0.04288848853482574, "n_trades": 544}, {"layer": "B2_canslim", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Khong cook OOS; denser Sharpe -0.84 giu trong DECISIONS. Execution Close T+1; risk = inverse-vol normalize + w_max.</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FINAL research mode. Khong cook OOS; denser Sharpe -0.84 giu trong DECISIONS. Execution Close T+1; risk = inverse-vol normalize + w_max.</t>
         </is>
       </c>
     </row>

--- a/store/backtest_report.xlsx
+++ b/store/backtest_report.xlsx
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>49.505</v>
+        <v>48.5149</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -504,7 +504,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.7311</v>
+        <v>0.6359</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -525,7 +525,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1517</v>
+        <v>1.9639</v>
       </c>
       <c r="F5" t="n">
         <v>22.5543</v>
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.1423</v>
+        <v>-5.22</v>
       </c>
       <c r="F6" t="n">
         <v>-17.8404</v>
@@ -573,7 +573,7 @@
         <v/>
       </c>
       <c r="E7" t="n">
-        <v>1.186539</v>
+        <v>1.110655</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -594,7 +594,7 @@
         <v/>
       </c>
       <c r="E8" t="n">
-        <v>0.5207310000000001</v>
+        <v>0.479044</v>
       </c>
       <c r="F8" t="n">
         <v>1.81868</v>
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4214</v>
+        <v>4.0317</v>
       </c>
       <c r="F9" t="n">
         <v>51.1841</v>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="E10" t="n">
-        <v>0.599473</v>
+        <v>0.554985</v>
       </c>
       <c r="F10" t="n">
         <v>1.903048</v>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="E11" t="n">
-        <v>0.859815</v>
+        <v>0.772352</v>
       </c>
       <c r="F11" t="n">
         <v>2.868998</v>
@@ -688,7 +688,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>32.1245</v>
+        <v>31.9566</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[{"layer": "B0_buyhold", "sharpe": 1.8321692424745784, "cagr": 0.5536251775534435, "max_drawdown": -0.19842368333185867, "n_trades": 0}, {"layer": "fundamental", "sharpe": 1.6093930295482695, "cagr": 0.49110361326245866, "max_drawdown": -0.214859956680571, "n_trades": 0}, {"layer": "regime", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}, {"layer": "alpha", "sharpe": 0.8521106914728611, "cagr": 0.08236888909752338, "max_drawdown": -0.04927282879075445, "n_trades": 96}, {"layer": "risk", "sharpe": 0.5207306915927736, "cagr": 0.044213977053179754, "max_drawdown": -0.051422689765345364, "n_trades": 101}, {"layer": "B1_ta", "sharpe": 2.74139086012495, "cagr": 0.2941371053925228, "max_drawdown": -0.04288848853482574, "n_trades": 544}, {"layer": "B2_canslim", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}]</t>
+          <t>[{"layer": "B0_buyhold", "sharpe": 1.8321692424745784, "cagr": 0.5536251775534435, "max_drawdown": -0.19842368333185867, "n_trades": 0}, {"layer": "fundamental", "sharpe": 1.6093930295482695, "cagr": 0.49110361326245866, "max_drawdown": -0.214859956680571, "n_trades": 0}, {"layer": "regime", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}, {"layer": "alpha", "sharpe": 0.8521106914728611, "cagr": 0.08236888909752338, "max_drawdown": -0.04927282879075445, "n_trades": 96}, {"layer": "risk", "sharpe": 0.516597336359449, "cagr": 0.04406431880488171, "max_drawdown": -0.05140911597644471, "n_trades": 100}, {"layer": "B1_ta", "sharpe": 2.74139086012495, "cagr": 0.2941371053925228, "max_drawdown": -0.04288848853482574, "n_trades": 544}, {"layer": "B2_canslim", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}]</t>
         </is>
       </c>
     </row>

--- a/store/backtest_report.xlsx
+++ b/store/backtest_report.xlsx
@@ -464,13 +464,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>542</v>
+        <v>618</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -485,11 +485,9 @@
         <v/>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v/>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>48.5149</v>
+        <v>49.0196</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -504,7 +502,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.6359</v>
+        <v>0.65</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -519,13 +517,13 @@
         <v>24.1421</v>
       </c>
       <c r="C5" t="n">
-        <v>13.4997</v>
+        <v>6.3826</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>28.8841</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9639</v>
+        <v>1.8698</v>
       </c>
       <c r="F5" t="n">
         <v>22.5543</v>
@@ -544,13 +542,13 @@
         <v>-19.883</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.2913</v>
+        <v>-8.928800000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-18.2913</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.22</v>
+        <v>-5.2212</v>
       </c>
       <c r="F6" t="n">
         <v>-17.8404</v>
@@ -569,11 +567,9 @@
         <v/>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v/>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>1.110655</v>
+        <v>1.103193</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -588,13 +584,13 @@
         <v>1.826156</v>
       </c>
       <c r="C8" t="n">
-        <v>2.732686</v>
+        <v>1.084355</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>2.063585</v>
       </c>
       <c r="E8" t="n">
-        <v>0.479044</v>
+        <v>0.458478</v>
       </c>
       <c r="F8" t="n">
         <v>1.81868</v>
@@ -613,13 +609,13 @@
         <v>55.1914</v>
       </c>
       <c r="C9" t="n">
-        <v>29.3491</v>
+        <v>13.3986</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>67.4764</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0317</v>
+        <v>3.8367</v>
       </c>
       <c r="F9" t="n">
         <v>51.1841</v>
@@ -638,13 +634,13 @@
         <v>1.855556</v>
       </c>
       <c r="C10" t="n">
-        <v>2.786177</v>
+        <v>1.078547</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>2.11591</v>
       </c>
       <c r="E10" t="n">
-        <v>0.554985</v>
+        <v>0.529936</v>
       </c>
       <c r="F10" t="n">
         <v>1.903048</v>
@@ -663,13 +659,13 @@
         <v>2.775808</v>
       </c>
       <c r="C11" t="n">
-        <v>6.839218</v>
+        <v>1.500598</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>3.688986</v>
       </c>
       <c r="E11" t="n">
-        <v>0.772352</v>
+        <v>0.73482</v>
       </c>
       <c r="F11" t="n">
         <v>2.868998</v>
@@ -688,7 +684,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>31.9566</v>
+        <v>31.9376</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -703,10 +699,10 @@
         <v>0.4973</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9632</v>
+        <v>2.0803</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.5672</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
@@ -1034,7 +1030,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[{"layer": "B0_buyhold", "sharpe": 1.8321692424745784, "cagr": 0.5536251775534435, "max_drawdown": -0.19842368333185867, "n_trades": 0}, {"layer": "fundamental", "sharpe": 1.6093930295482695, "cagr": 0.49110361326245866, "max_drawdown": -0.214859956680571, "n_trades": 0}, {"layer": "regime", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}, {"layer": "alpha", "sharpe": 0.8521106914728611, "cagr": 0.08236888909752338, "max_drawdown": -0.04927282879075445, "n_trades": 96}, {"layer": "risk", "sharpe": 0.516597336359449, "cagr": 0.04406431880488171, "max_drawdown": -0.05140911597644471, "n_trades": 100}, {"layer": "B1_ta", "sharpe": 2.74139086012495, "cagr": 0.2941371053925228, "max_drawdown": -0.04288848853482574, "n_trades": 544}, {"layer": "B2_canslim", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}]</t>
+          <t>[{"layer": "B0_buyhold", "sharpe": 1.8321692424745784, "cagr": 0.5536251775534435, "max_drawdown": -0.19842368333185867, "n_trades": 0}, {"layer": "fundamental", "sharpe": 1.6093930295482695, "cagr": 0.49110361326245866, "max_drawdown": -0.214859956680571, "n_trades": 0}, {"layer": "regime", "sharpe": null, "cagr": 0.0, "max_drawdown": 0.0, "n_trades": 0}, {"layer": "alpha", "sharpe": 0.8521106914728611, "cagr": 0.08236888909752338, "max_drawdown": -0.04927282879075445, "n_trades": 96}, {"layer": "risk", "sharpe": 0.516597336359449, "cagr": 0.04406431880488171, "max_drawdown": -0.05140911597644471, "n_trades": 100}, {"layer": "B1_ta", "sharpe": 1.0725592315305976, "cagr": 0.13253833286733352, "max_drawdown": -0.08980622598993593, "n_trades": 621}, {"layer": "B2_canslim", "sharpe": 2.0446126657566954, "cagr": 0.6658630515344468, "max_drawdown": -0.18453103375416424, "n_trades": 120}]</t>
         </is>
       </c>
     </row>
